--- a/Projects/sglt2-cardiac-surgery/registration/prospero/prospero_final.xlsx
+++ b/Projects/sglt2-cardiac-surgery/registration/prospero/prospero_final.xlsx
@@ -1,32 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jason\Projects\srma-agent-toolkit\Projects\sglt2-cardiac-surgery\registration\prospero\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jason\Projects\srma-agent-toolkit\projects\sglt2-cardiac-surgery\registration\prospero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F51A1FD-F946-4917-A2CC-3FE3738FF17F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9178C21-B0F6-4A98-9CEC-7CC5DE700C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28740" yWindow="-60" windowWidth="28920" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PROSPERO_Form" sheetId="1" r:id="rId1"/>
     <sheet name="Field_Map" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="234">
   <si>
     <t>PROSPERO Universal Registration Form</t>
   </si>
@@ -601,16 +596,10 @@
     <t>2026-08-15</t>
   </si>
   <si>
-    <t>Unpublished or ongoing studies will be considered when identified through planned sources or supplementary searching.</t>
-  </si>
-  <si>
     <t>No language restrictions are planned unless explicitly specified in the project configuration.</t>
   </si>
   <si>
     <t>No publication-date restrictions are planned unless explicitly specified in the project configuration.</t>
-  </si>
-  <si>
-    <t>Reference lists of included studies and relevant reviews will be checked for additional eligible studies.</t>
   </si>
   <si>
     <t>AUTHOR CHECK REQUIRED: Add the final public link/URL to the search strategy if applicable.</t>
@@ -710,10 +699,6 @@
   </si>
   <si>
     <t>AUTO + EDITED</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>South Korea</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
@@ -800,6 +785,22 @@
   </si>
   <si>
     <t>Sodium-Glucose Transporter 2 Inhibitors; Cardiac Surgical Procedures; Acute Kidney Injury; Perioperative Care; Postoperative Complications</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Although SGLT2 inhibitors have well-established cardiorenal benefits in other clinical settings, their perioperative effects in adult cardiac surgery remain uncertain. In particular, the effect of perioperative SGLT2 inhibitor exposure on postoperative acute kidney injury has not been clearly established. This review will synthesize randomized and observational evidence, with primary quantitative emphasis on acute kidney injury and randomized controlled trials, while also evaluating other relevant postoperative efficacy and safety outcomes. The review aims to clarify the current evidence base and its implications for perioperative SGLT2 inhibitor use in adult cardiac surgery.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Republic of Korea</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unpublished or ongoing studies will be considered when identified through planned sources or supplementary searching.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reference lists of included studies and relevant reviews will be checked for additional eligible studies.</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -946,21 +947,21 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1260,97 +1261,97 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F136"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" customWidth="1"/>
-    <col min="2" max="4" width="16.7109375" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" customWidth="1"/>
+    <col min="1" max="1" width="28.73046875" customWidth="1"/>
+    <col min="2" max="4" width="16.73046875" customWidth="1"/>
+    <col min="5" max="5" width="12.73046875" customWidth="1"/>
+    <col min="6" max="6" width="22.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A7" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
       <c r="E8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
       <c r="E11" s="1" t="s">
         <v>3</v>
       </c>
@@ -1358,21 +1359,23 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A13" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A14" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
       <c r="E14" s="1" t="s">
         <v>3</v>
       </c>
@@ -1380,47 +1383,47 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A16" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
+        <v>207</v>
+      </c>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
       <c r="E17" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F17" s="9" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
+      <c r="F17" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
+        <v>223</v>
+      </c>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
       <c r="E20" s="1" t="s">
         <v>3</v>
       </c>
@@ -1428,23 +1431,23 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A22" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
+        <v>231</v>
+      </c>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
       <c r="E23" s="1" t="s">
         <v>3</v>
       </c>
@@ -1452,33 +1455,33 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A25" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A27" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
+        <v>208</v>
+      </c>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
       <c r="E27" s="1" t="s">
         <v>3</v>
       </c>
@@ -1486,23 +1489,23 @@
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A29" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A30" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
+        <v>209</v>
+      </c>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
       <c r="E30" s="1" t="s">
         <v>3</v>
       </c>
@@ -1510,23 +1513,23 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A32" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A33" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
+        <v>210</v>
+      </c>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
       <c r="E33" s="1" t="s">
         <v>3</v>
       </c>
@@ -1534,23 +1537,23 @@
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A35" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A36" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
+        <v>211</v>
+      </c>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
       <c r="E36" s="1" t="s">
         <v>3</v>
       </c>
@@ -1558,23 +1561,23 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="s">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A38" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A39" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
+        <v>212</v>
+      </c>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
       <c r="E39" s="1" t="s">
         <v>3</v>
       </c>
@@ -1582,33 +1585,33 @@
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A41" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A42" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A43" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
+        <v>213</v>
+      </c>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
       <c r="E43" s="1" t="s">
         <v>3</v>
       </c>
@@ -1616,33 +1619,33 @@
         <v>19</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="4" t="s">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A45" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A46" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="6" t="s">
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A47" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
       <c r="E47" s="1" t="s">
         <v>3</v>
       </c>
@@ -1650,23 +1653,23 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="8" t="s">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A49" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A50" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="B49" s="5"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B50" s="6"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
+      <c r="B50" s="8"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
       <c r="E50" s="1" t="s">
         <v>3</v>
       </c>
@@ -1674,33 +1677,33 @@
         <v>19</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="4" t="s">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A52" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
+      <c r="B52" s="5"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A53" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B53" s="5"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="5"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B53" s="6"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A54" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="B54" s="6"/>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
+        <v>217</v>
+      </c>
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
       <c r="E54" s="1" t="s">
         <v>3</v>
       </c>
@@ -1708,153 +1711,153 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="4" t="s">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A56" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="5" t="s">
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="5"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A57" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B57" s="5"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="6" t="s">
+      <c r="B57" s="6"/>
+      <c r="C57" s="6"/>
+      <c r="D57" s="6"/>
+      <c r="E57" s="6"/>
+      <c r="F57" s="6"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A58" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="B58" s="8"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="8"/>
+      <c r="E58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A60" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B60" s="6"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="6"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A61" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="B61" s="8"/>
+      <c r="C61" s="8"/>
+      <c r="D61" s="8"/>
+      <c r="E61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A63" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B63" s="6"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="6"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A64" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="B58" s="6"/>
-      <c r="C58" s="6"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="B61" s="6"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
-      <c r="E61" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="6" t="s">
+      <c r="B64" s="8"/>
+      <c r="C64" s="8"/>
+      <c r="D64" s="8"/>
+      <c r="E64" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A66" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B66" s="6"/>
+      <c r="C66" s="6"/>
+      <c r="D66" s="6"/>
+      <c r="E66" s="6"/>
+      <c r="F66" s="6"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A67" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="B64" s="6"/>
-      <c r="C64" s="6"/>
-      <c r="D64" s="6"/>
-      <c r="E64" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="5"/>
-      <c r="E66" s="5"/>
-      <c r="F66" s="5"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="6" t="s">
+      <c r="B67" s="8"/>
+      <c r="C67" s="8"/>
+      <c r="D67" s="8"/>
+      <c r="E67" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A69" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B69" s="6"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="6"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A70" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="B70" s="8"/>
+      <c r="C70" s="8"/>
+      <c r="D70" s="8"/>
+      <c r="E70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A72" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B72" s="6"/>
+      <c r="C72" s="6"/>
+      <c r="D72" s="6"/>
+      <c r="E72" s="6"/>
+      <c r="F72" s="6"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A73" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="B67" s="6"/>
-      <c r="C67" s="6"/>
-      <c r="D67" s="6"/>
-      <c r="E67" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B69" s="5"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="5"/>
-      <c r="E69" s="5"/>
-      <c r="F69" s="5"/>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="B70" s="6"/>
-      <c r="C70" s="6"/>
-      <c r="D70" s="6"/>
-      <c r="E70" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="B73" s="6"/>
-      <c r="C73" s="6"/>
-      <c r="D73" s="6"/>
+      <c r="B73" s="8"/>
+      <c r="C73" s="8"/>
+      <c r="D73" s="8"/>
       <c r="E73" s="1" t="s">
         <v>3</v>
       </c>
@@ -1862,153 +1865,153 @@
         <v>19</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="5" t="s">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A75" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
-      <c r="D75" s="5"/>
-      <c r="E75" s="5"/>
-      <c r="F75" s="5"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="6" t="s">
+      <c r="B75" s="6"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="6"/>
+      <c r="E75" s="6"/>
+      <c r="F75" s="6"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A76" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="B76" s="8"/>
+      <c r="C76" s="8"/>
+      <c r="D76" s="8"/>
+      <c r="E76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A78" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B78" s="6"/>
+      <c r="C78" s="6"/>
+      <c r="D78" s="6"/>
+      <c r="E78" s="6"/>
+      <c r="F78" s="6"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A79" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="B79" s="8"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="8"/>
+      <c r="E79" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A81" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B81" s="5"/>
+      <c r="C81" s="5"/>
+      <c r="D81" s="5"/>
+      <c r="E81" s="5"/>
+      <c r="F81" s="5"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A82" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B82" s="6"/>
+      <c r="C82" s="6"/>
+      <c r="D82" s="6"/>
+      <c r="E82" s="6"/>
+      <c r="F82" s="6"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A83" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="B76" s="6"/>
-      <c r="C76" s="6"/>
-      <c r="D76" s="6"/>
-      <c r="E76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B78" s="5"/>
-      <c r="C78" s="5"/>
-      <c r="D78" s="5"/>
-      <c r="E78" s="5"/>
-      <c r="F78" s="5"/>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="6" t="s">
+      <c r="B83" s="8"/>
+      <c r="C83" s="8"/>
+      <c r="D83" s="8"/>
+      <c r="E83" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A85" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B85" s="6"/>
+      <c r="C85" s="6"/>
+      <c r="D85" s="6"/>
+      <c r="E85" s="6"/>
+      <c r="F85" s="6"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A86" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="B79" s="6"/>
-      <c r="C79" s="6"/>
-      <c r="D79" s="6"/>
-      <c r="E79" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B81" s="4"/>
-      <c r="C81" s="4"/>
-      <c r="D81" s="4"/>
-      <c r="E81" s="4"/>
-      <c r="F81" s="4"/>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B82" s="5"/>
-      <c r="C82" s="5"/>
-      <c r="D82" s="5"/>
-      <c r="E82" s="5"/>
-      <c r="F82" s="5"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="6" t="s">
+      <c r="B86" s="8"/>
+      <c r="C86" s="8"/>
+      <c r="D86" s="8"/>
+      <c r="E86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A88" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B88" s="6"/>
+      <c r="C88" s="6"/>
+      <c r="D88" s="6"/>
+      <c r="E88" s="6"/>
+      <c r="F88" s="6"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A89" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="B83" s="6"/>
-      <c r="C83" s="6"/>
-      <c r="D83" s="6"/>
-      <c r="E83" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B85" s="5"/>
-      <c r="C85" s="5"/>
-      <c r="D85" s="5"/>
-      <c r="E85" s="5"/>
-      <c r="F85" s="5"/>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="6" t="s">
+      <c r="B89" s="8"/>
+      <c r="C89" s="8"/>
+      <c r="D89" s="8"/>
+      <c r="E89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A91" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B91" s="6"/>
+      <c r="C91" s="6"/>
+      <c r="D91" s="6"/>
+      <c r="E91" s="6"/>
+      <c r="F91" s="6"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A92" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="B86" s="6"/>
-      <c r="C86" s="6"/>
-      <c r="D86" s="6"/>
-      <c r="E86" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B88" s="5"/>
-      <c r="C88" s="5"/>
-      <c r="D88" s="5"/>
-      <c r="E88" s="5"/>
-      <c r="F88" s="5"/>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="B89" s="6"/>
-      <c r="C89" s="6"/>
-      <c r="D89" s="6"/>
-      <c r="E89" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B91" s="5"/>
-      <c r="C91" s="5"/>
-      <c r="D91" s="5"/>
-      <c r="E91" s="5"/>
-      <c r="F91" s="5"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="B92" s="6"/>
-      <c r="C92" s="6"/>
-      <c r="D92" s="6"/>
+      <c r="B92" s="8"/>
+      <c r="C92" s="8"/>
+      <c r="D92" s="8"/>
       <c r="E92" s="1" t="s">
         <v>3</v>
       </c>
@@ -2016,33 +2019,33 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="4" t="s">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A94" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B94" s="4"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="4"/>
-      <c r="E94" s="4"/>
-      <c r="F94" s="4"/>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="5" t="s">
+      <c r="B94" s="5"/>
+      <c r="C94" s="5"/>
+      <c r="D94" s="5"/>
+      <c r="E94" s="5"/>
+      <c r="F94" s="5"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A95" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B95" s="5"/>
-      <c r="C95" s="5"/>
-      <c r="D95" s="5"/>
-      <c r="E95" s="5"/>
-      <c r="F95" s="5"/>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B95" s="6"/>
+      <c r="C95" s="6"/>
+      <c r="D95" s="6"/>
+      <c r="E95" s="6"/>
+      <c r="F95" s="6"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A96" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="B96" s="6"/>
-      <c r="C96" s="6"/>
-      <c r="D96" s="6"/>
+        <v>215</v>
+      </c>
+      <c r="B96" s="8"/>
+      <c r="C96" s="8"/>
+      <c r="D96" s="8"/>
       <c r="E96" s="1" t="s">
         <v>3</v>
       </c>
@@ -2050,23 +2053,23 @@
         <v>19</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98" s="5" t="s">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A98" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B98" s="5"/>
-      <c r="C98" s="5"/>
-      <c r="D98" s="5"/>
-      <c r="E98" s="5"/>
-      <c r="F98" s="5"/>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B98" s="6"/>
+      <c r="C98" s="6"/>
+      <c r="D98" s="6"/>
+      <c r="E98" s="6"/>
+      <c r="F98" s="6"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A99" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="B99" s="6"/>
-      <c r="C99" s="6"/>
-      <c r="D99" s="6"/>
+        <v>216</v>
+      </c>
+      <c r="B99" s="8"/>
+      <c r="C99" s="8"/>
+      <c r="D99" s="8"/>
       <c r="E99" s="1" t="s">
         <v>3</v>
       </c>
@@ -2074,33 +2077,33 @@
         <v>19</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A101" s="4" t="s">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A101" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B101" s="4"/>
-      <c r="C101" s="4"/>
-      <c r="D101" s="4"/>
-      <c r="E101" s="4"/>
-      <c r="F101" s="4"/>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A102" s="5" t="s">
+      <c r="B101" s="5"/>
+      <c r="C101" s="5"/>
+      <c r="D101" s="5"/>
+      <c r="E101" s="5"/>
+      <c r="F101" s="5"/>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A102" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B102" s="5"/>
-      <c r="C102" s="5"/>
-      <c r="D102" s="5"/>
-      <c r="E102" s="5"/>
-      <c r="F102" s="5"/>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B102" s="6"/>
+      <c r="C102" s="6"/>
+      <c r="D102" s="6"/>
+      <c r="E102" s="6"/>
+      <c r="F102" s="6"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A103" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B103" s="6"/>
-      <c r="C103" s="6"/>
-      <c r="D103" s="6"/>
+        <v>214</v>
+      </c>
+      <c r="B103" s="8"/>
+      <c r="C103" s="8"/>
+      <c r="D103" s="8"/>
       <c r="E103" s="1" t="s">
         <v>3</v>
       </c>
@@ -2108,33 +2111,33 @@
         <v>4</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" s="4" t="s">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A105" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B105" s="4"/>
-      <c r="C105" s="4"/>
-      <c r="D105" s="4"/>
-      <c r="E105" s="4"/>
-      <c r="F105" s="4"/>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" s="5" t="s">
+      <c r="B105" s="5"/>
+      <c r="C105" s="5"/>
+      <c r="D105" s="5"/>
+      <c r="E105" s="5"/>
+      <c r="F105" s="5"/>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A106" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B106" s="5"/>
-      <c r="C106" s="5"/>
-      <c r="D106" s="5"/>
-      <c r="E106" s="5"/>
-      <c r="F106" s="5"/>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A107" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="B107" s="6"/>
-      <c r="C107" s="6"/>
-      <c r="D107" s="6"/>
+      <c r="B106" s="6"/>
+      <c r="C106" s="6"/>
+      <c r="D106" s="6"/>
+      <c r="E106" s="6"/>
+      <c r="F106" s="6"/>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A107" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="B107" s="8"/>
+      <c r="C107" s="8"/>
+      <c r="D107" s="8"/>
       <c r="E107" s="1" t="s">
         <v>3</v>
       </c>
@@ -2142,23 +2145,23 @@
         <v>4</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A109" s="5" t="s">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A109" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B109" s="5"/>
-      <c r="C109" s="5"/>
-      <c r="D109" s="5"/>
-      <c r="E109" s="5"/>
-      <c r="F109" s="5"/>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A110" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="B110" s="6"/>
-      <c r="C110" s="6"/>
-      <c r="D110" s="6"/>
+      <c r="B109" s="6"/>
+      <c r="C109" s="6"/>
+      <c r="D109" s="6"/>
+      <c r="E109" s="6"/>
+      <c r="F109" s="6"/>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A110" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="B110" s="8"/>
+      <c r="C110" s="8"/>
+      <c r="D110" s="8"/>
       <c r="E110" s="1" t="s">
         <v>3</v>
       </c>
@@ -2166,33 +2169,33 @@
         <v>4</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112" s="4" t="s">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A112" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B112" s="4"/>
-      <c r="C112" s="4"/>
-      <c r="D112" s="4"/>
-      <c r="E112" s="4"/>
-      <c r="F112" s="4"/>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113" s="5" t="s">
+      <c r="B112" s="5"/>
+      <c r="C112" s="5"/>
+      <c r="D112" s="5"/>
+      <c r="E112" s="5"/>
+      <c r="F112" s="5"/>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A113" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B113" s="5"/>
-      <c r="C113" s="5"/>
-      <c r="D113" s="5"/>
-      <c r="E113" s="5"/>
-      <c r="F113" s="5"/>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B113" s="6"/>
+      <c r="C113" s="6"/>
+      <c r="D113" s="6"/>
+      <c r="E113" s="6"/>
+      <c r="F113" s="6"/>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A114" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="B114" s="6"/>
-      <c r="C114" s="6"/>
-      <c r="D114" s="6"/>
+        <v>226</v>
+      </c>
+      <c r="B114" s="8"/>
+      <c r="C114" s="8"/>
+      <c r="D114" s="8"/>
       <c r="E114" s="1" t="s">
         <v>3</v>
       </c>
@@ -2200,23 +2203,23 @@
         <v>19</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A116" s="5" t="s">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A116" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B116" s="5"/>
-      <c r="C116" s="5"/>
-      <c r="D116" s="5"/>
-      <c r="E116" s="5"/>
-      <c r="F116" s="5"/>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B116" s="6"/>
+      <c r="C116" s="6"/>
+      <c r="D116" s="6"/>
+      <c r="E116" s="6"/>
+      <c r="F116" s="6"/>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A117" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="B117" s="6"/>
-      <c r="C117" s="6"/>
-      <c r="D117" s="6"/>
+        <v>227</v>
+      </c>
+      <c r="B117" s="8"/>
+      <c r="C117" s="8"/>
+      <c r="D117" s="8"/>
       <c r="E117" s="1" t="s">
         <v>3</v>
       </c>
@@ -2224,23 +2227,23 @@
         <v>19</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A119" s="5" t="s">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A119" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B119" s="5"/>
-      <c r="C119" s="5"/>
-      <c r="D119" s="5"/>
-      <c r="E119" s="5"/>
-      <c r="F119" s="5"/>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B119" s="6"/>
+      <c r="C119" s="6"/>
+      <c r="D119" s="6"/>
+      <c r="E119" s="6"/>
+      <c r="F119" s="6"/>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A120" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="B120" s="6"/>
-      <c r="C120" s="6"/>
-      <c r="D120" s="6"/>
+        <v>225</v>
+      </c>
+      <c r="B120" s="8"/>
+      <c r="C120" s="8"/>
+      <c r="D120" s="8"/>
       <c r="E120" s="1" t="s">
         <v>3</v>
       </c>
@@ -2248,23 +2251,23 @@
         <v>19</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A122" s="5" t="s">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A122" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B122" s="5"/>
-      <c r="C122" s="5"/>
-      <c r="D122" s="5"/>
-      <c r="E122" s="5"/>
-      <c r="F122" s="5"/>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A123" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="B123" s="6"/>
-      <c r="C123" s="6"/>
-      <c r="D123" s="6"/>
+      <c r="B122" s="6"/>
+      <c r="C122" s="6"/>
+      <c r="D122" s="6"/>
+      <c r="E122" s="6"/>
+      <c r="F122" s="6"/>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A123" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="B123" s="8"/>
+      <c r="C123" s="8"/>
+      <c r="D123" s="8"/>
       <c r="E123" s="1" t="s">
         <v>3</v>
       </c>
@@ -2272,33 +2275,33 @@
         <v>4</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A125" s="4" t="s">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A125" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B125" s="4"/>
-      <c r="C125" s="4"/>
-      <c r="D125" s="4"/>
-      <c r="E125" s="4"/>
-      <c r="F125" s="4"/>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A126" s="5" t="s">
+      <c r="B125" s="5"/>
+      <c r="C125" s="5"/>
+      <c r="D125" s="5"/>
+      <c r="E125" s="5"/>
+      <c r="F125" s="5"/>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A126" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B126" s="5"/>
-      <c r="C126" s="5"/>
-      <c r="D126" s="5"/>
-      <c r="E126" s="5"/>
-      <c r="F126" s="5"/>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A127" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="B127" s="6"/>
-      <c r="C127" s="6"/>
-      <c r="D127" s="6"/>
+      <c r="B126" s="6"/>
+      <c r="C126" s="6"/>
+      <c r="D126" s="6"/>
+      <c r="E126" s="6"/>
+      <c r="F126" s="6"/>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A127" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="B127" s="8"/>
+      <c r="C127" s="8"/>
+      <c r="D127" s="8"/>
       <c r="E127" s="1" t="s">
         <v>3</v>
       </c>
@@ -2306,23 +2309,23 @@
         <v>4</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A129" s="5" t="s">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A129" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B129" s="5"/>
-      <c r="C129" s="5"/>
-      <c r="D129" s="5"/>
-      <c r="E129" s="5"/>
-      <c r="F129" s="5"/>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B129" s="6"/>
+      <c r="C129" s="6"/>
+      <c r="D129" s="6"/>
+      <c r="E129" s="6"/>
+      <c r="F129" s="6"/>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A130" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="B130" s="6"/>
-      <c r="C130" s="6"/>
-      <c r="D130" s="6"/>
+        <v>224</v>
+      </c>
+      <c r="B130" s="8"/>
+      <c r="C130" s="8"/>
+      <c r="D130" s="8"/>
       <c r="E130" s="1" t="s">
         <v>3</v>
       </c>
@@ -2330,23 +2333,23 @@
         <v>19</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A132" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="B132" s="5"/>
-      <c r="C132" s="5"/>
-      <c r="D132" s="5"/>
-      <c r="E132" s="5"/>
-      <c r="F132" s="5"/>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A132" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="B132" s="6"/>
+      <c r="C132" s="6"/>
+      <c r="D132" s="6"/>
+      <c r="E132" s="6"/>
+      <c r="F132" s="6"/>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A133" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="B133" s="6"/>
-      <c r="C133" s="6"/>
-      <c r="D133" s="6"/>
+        <v>229</v>
+      </c>
+      <c r="B133" s="8"/>
+      <c r="C133" s="8"/>
+      <c r="D133" s="8"/>
       <c r="E133" s="1" t="s">
         <v>3</v>
       </c>
@@ -2354,21 +2357,21 @@
         <v>19</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A135" s="5" t="s">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A135" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B135" s="5"/>
-      <c r="C135" s="5"/>
-      <c r="D135" s="5"/>
-      <c r="E135" s="5"/>
-      <c r="F135" s="5"/>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" s="6"/>
-      <c r="B136" s="6"/>
-      <c r="C136" s="6"/>
-      <c r="D136" s="6"/>
+      <c r="B135" s="6"/>
+      <c r="C135" s="6"/>
+      <c r="D135" s="6"/>
+      <c r="E135" s="6"/>
+      <c r="F135" s="6"/>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A136" s="8"/>
+      <c r="B136" s="8"/>
+      <c r="C136" s="8"/>
+      <c r="D136" s="8"/>
       <c r="E136" s="1" t="s">
         <v>3</v>
       </c>
@@ -2488,9 +2491,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G42"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>58</v>
       </c>
@@ -2513,7 +2516,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>65</v>
       </c>
@@ -2536,7 +2539,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>69</v>
       </c>
@@ -2559,7 +2562,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>72</v>
       </c>
@@ -2582,7 +2585,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>75</v>
       </c>
@@ -2605,7 +2608,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>78</v>
       </c>
@@ -2628,7 +2631,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>81</v>
       </c>
@@ -2651,7 +2654,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>84</v>
       </c>
@@ -2674,7 +2677,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>87</v>
       </c>
@@ -2697,7 +2700,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>90</v>
       </c>
@@ -2720,7 +2723,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>93</v>
       </c>
@@ -2743,7 +2746,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>96</v>
       </c>
@@ -2766,7 +2769,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>99</v>
       </c>
@@ -2789,7 +2792,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>102</v>
       </c>
@@ -2812,7 +2815,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>105</v>
       </c>
@@ -2835,7 +2838,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>108</v>
       </c>
@@ -2858,7 +2861,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>111</v>
       </c>
@@ -2881,7 +2884,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>114</v>
       </c>
@@ -2904,7 +2907,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>117</v>
       </c>
@@ -2927,7 +2930,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>120</v>
       </c>
@@ -2950,7 +2953,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>123</v>
       </c>
@@ -2973,7 +2976,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>126</v>
       </c>
@@ -2996,7 +2999,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>129</v>
       </c>
@@ -3019,7 +3022,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>132</v>
       </c>
@@ -3042,7 +3045,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>135</v>
       </c>
@@ -3065,7 +3068,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>138</v>
       </c>
@@ -3088,7 +3091,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>141</v>
       </c>
@@ -3111,7 +3114,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>144</v>
       </c>
@@ -3134,7 +3137,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>147</v>
       </c>
@@ -3157,7 +3160,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>150</v>
       </c>
@@ -3180,7 +3183,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>153</v>
       </c>
@@ -3203,7 +3206,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>156</v>
       </c>
@@ -3226,7 +3229,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>159</v>
       </c>
@@ -3249,7 +3252,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>162</v>
       </c>
@@ -3272,7 +3275,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>165</v>
       </c>
@@ -3295,7 +3298,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>168</v>
       </c>
@@ -3318,7 +3321,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>171</v>
       </c>
@@ -3341,7 +3344,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>174</v>
       </c>
@@ -3364,7 +3367,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>177</v>
       </c>
@@ -3387,7 +3390,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>180</v>
       </c>
@@ -3410,7 +3413,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>183</v>
       </c>
@@ -3433,7 +3436,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>186</v>
       </c>
